--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -543,29 +543,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>salons in Jaipur</t>
+          <t>gyms in Jaipur</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Unisex Salon By Nidhi</t>
+          <t>KLEAN FIT Iconic C-SCHEME</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>34-A,Raghu Vihar Vistar,Near VT Road, Chauraha, Patrkar Road, Mansarovar, Jaipur, Rajasthan 302020, India</t>
+          <t>3rd Floor, Crystal Palm Mall, 22 Godown Circle, Sardar Patel Marg, near Nehru Sahkar Bhavan, Shivaji Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>098871 81819</t>
+          <t>090246 62515</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1403</v>
+        <v>889</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -586,29 +586,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>clinics in Jaipur</t>
+          <t>gyms in Jaipur</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SHRI BALAJI HOSPITAL</t>
+          <t>Lifetime Fitness Club</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>38,39, TIRUPATI FLATS B, Niwaru Rd, Rajendra Nagar, Harnathapura, Jhotwara, Jaipur, Rajasthan 302012, India</t>
+          <t>3rd Floor, at V Cube, Plot no. 1-6, opp. Gaurav Tower Marg, Kalyan Colony, D-Block, Malviya Nagar, Jaipur, Rajasthan 302017, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>096723 74725</t>
+          <t>099505 50885</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>487</v>
+        <v>756</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -629,29 +629,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>salons in Jaipur</t>
+          <t>gyms in Jaipur</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>The tony's hair &amp;beauty unisex salon</t>
+          <t>Burnfit gym | Best Gym In Jaipur</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Shop no 56, gate no. 2, Sardar Patel Marg, opposite BSNL office, Patel Colony, Hathroi, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>Plot no. A-7, behind Mehta book depo, Telephone Colony, Bank Colony, Gopal Pura Mode, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302015, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>087428 79416</t>
+          <t>082906 01516</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -677,24 +677,24 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Dr. Ayush Multispeciality Clinic</t>
+          <t>Aura Skin &amp; Health Clinic</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>D- 429, Kesar Vihar, Siddharth Nagar, Malviya Nagar, Jaipur, Rajasthan 302017, India</t>
+          <t>J-108, Ashok Chowk, Adarsh Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302004, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>089555 47847</t>
+          <t>084400 66723</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>94</v>
+        <v>220</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -715,29 +715,29 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>salons in Jaipur</t>
+          <t>gyms in Jaipur</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Beyond Brunette - A Luxury Salon</t>
+          <t>Sweatup - The Luxury Gym</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Panchsheel Enclave, 79, Jawahar Lal Nehru Marg, behind Clarks Amer Hotel, Vishnu Enclave, Chandrakala Colony, Durgapura, Jaipur, Rajasthan 302017, India</t>
+          <t>E-10, Gautam Marg, Amrapali Circle, Vaishali Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302021, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>077377 78513</t>
+          <t>070822 40402</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beyond_brunette?igsh=bGIyZ2xxamRpOW9q/</t>
+          <t>https://www.instagram.com/sweatup__theluxurygym/</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -548,24 +548,24 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>KLEAN FIT Iconic C-SCHEME</t>
+          <t>Fitness Pulse Gym</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>3rd Floor, Crystal Palm Mall, 22 Godown Circle, Sardar Patel Marg, near Nehru Sahkar Bhavan, Shivaji Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>Kalwar Rd, Suraj Nagar, Jhotwara, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302012, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>090246 62515</t>
+          <t>098870 00058</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>889</v>
+        <v>1925</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -591,24 +591,24 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Lifetime Fitness Club</t>
+          <t>UFC GYM Mansarovar, Jaipur</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>3rd Floor, at V Cube, Plot no. 1-6, opp. Gaurav Tower Marg, Kalyan Colony, D-Block, Malviya Nagar, Jaipur, Rajasthan 302017, India</t>
+          <t>4th floor, Sunny Trade Center, Gangaram Nagar, New Aatish Market, Shanthi Nagar, Mansarovar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302020, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>099505 50885</t>
+          <t>073000 09012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>756</v>
+        <v>557</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -629,29 +629,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>salons in Jaipur</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Burnfit gym | Best Gym In Jaipur</t>
+          <t>BARBER UNISEX SALON</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Plot no. A-7, behind Mehta book depo, Telephone Colony, Bank Colony, Gopal Pura Mode, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302015, India</t>
+          <t>S-4, Piller No - 46, near SBI Bank, opp. Ram Mandir, Hawa Sadak, Keshav Nagar, Civil Lines, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302006, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>082906 01516</t>
+          <t>096809 52469</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>253</v>
+        <v>517</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -672,29 +672,29 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>clinics in Jaipur</t>
+          <t>salons in Jaipur</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Aura Skin &amp; Health Clinic</t>
+          <t>Salon by Harsh unisex salon</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>J-108, Ashok Chowk, Adarsh Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302004, India</t>
+          <t>Lg 16a, Ananda Rd, near Aananda Road, Kankha Ki Dhani, Jaipur, Rajasthan 302020, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>084400 66723</t>
+          <t>096676 20423</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>220</v>
+        <v>507</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -720,24 +720,24 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Sweatup - The Luxury Gym</t>
+          <t>Jaipur fitness gym</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>E-10, Gautam Marg, Amrapali Circle, Vaishali Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302021, India</t>
+          <t>40, Nh-8 Bypass Rd, Gulzar Colony, Lal Dungri, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302002, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>070822 40402</t>
+          <t>088899 99076</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>316</v>
+        <v>148</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sweatup__theluxurygym/</t>
+          <t>https://www.instagram.com/jaipur_fitness_gym</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -548,24 +548,24 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Fitness Pulse Gym</t>
+          <t>Fitness Pro Elite Mansarovar</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Kalwar Rd, Suraj Nagar, Jhotwara, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302012, India</t>
+          <t>near IPS School, Shanthi Nagar B, Shanthi Nagar, Mansarovar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302019, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>098870 00058</t>
+          <t>093144 55664</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1925</v>
+        <v>1514</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -586,29 +586,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>salons in Jaipur</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>UFC GYM Mansarovar, Jaipur</t>
+          <t>K Factor Salon</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>4th floor, Sunny Trade Center, Gangaram Nagar, New Aatish Market, Shanthi Nagar, Mansarovar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302020, India</t>
+          <t>157, Ayodhya Path, Saket Nagar, Shyam Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302019, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>073000 09012</t>
+          <t>096806 56581</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
         <v>4.6</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>557</v>
+        <v>715</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -634,37 +634,41 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BARBER UNISEX SALON</t>
+          <t>Saundarya beauty salon and academy</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>S-4, Piller No - 46, near SBI Bank, opp. Ram Mandir, Hawa Sadak, Keshav Nagar, Civil Lines, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302006, India</t>
+          <t>6-A, Behind Maharwal Optical, Behind Vidhan Sabha Lal Kothi, Janpath Road, Friends Colony, Satya Vihar, Friends Colony, Krishna Nagar II, Lalkothi, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302015, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>096809 52469</t>
+          <t>098290 23927</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>517</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>1242</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/saundaryabeautysalon?igsh=dzJ4ZnZxd25zNjdt</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
@@ -672,42 +676,46 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>salons in Jaipur</t>
+          <t>gyms in Jaipur</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Salon by Harsh unisex salon</t>
+          <t>Sky Fitness - Best Gym in Mangyawas, Mansarovar, Jaipur</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Lg 16a, Ananda Rd, near Aananda Road, Kankha Ki Dhani, Jaipur, Rajasthan 302020, India</t>
+          <t>Maharani Garden Road, Mansarover, Rajat Path, Jaipur, Rajasthan 302020, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>096676 20423</t>
+          <t>095880 37686</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>507</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>188</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/skyfitnessjaipur</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
@@ -720,24 +728,24 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Jaipur fitness gym</t>
+          <t>Sky Fitness - Best Gym In Ajmer Road, Jaipur</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40, Nh-8 Bypass Rd, Gulzar Colony, Lal Dungri, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302002, India</t>
+          <t>1st Floor, ML Tower, Metro Piller No-01, Teja Circle, Gopalpura Bypass Rd, near Drom Marbel, Mohan Nagar, Mohru Nagar, Mansarovar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302020, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>088899 99076</t>
+          <t>075687 98310</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -752,7 +760,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jaipur_fitness_gym</t>
+          <t>https://www.instagram.com/skyfitnessjaipur1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -543,29 +543,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>restaurants in Jaipur</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Fitness Pro Elite Mansarovar</t>
+          <t>Handi restaurant jaipur</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>near IPS School, Shanthi Nagar B, Shanthi Nagar, Mansarovar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302019, India</t>
+          <t>Mirza Ismail Rd, opp. GPO, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>093144 55664</t>
+          <t>098291 74873</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1514</v>
+        <v>13152</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -586,29 +586,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>salons in Jaipur</t>
+          <t>clinics in Jaipur</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>K Factor Salon</t>
+          <t>Divinity total skin care</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>157, Ayodhya Path, Saket Nagar, Shyam Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302019, India</t>
+          <t>Kaveri Path, 21/280, Madhyam Marg, Mansarovar Sector 1, Mansarovar, Jaipur, Rajasthan 302020, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>096806 56581</t>
+          <t>095711 33151</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>715</v>
+        <v>1328</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -629,46 +629,42 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>salons in Jaipur</t>
+          <t>gyms in Jaipur</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Saundarya beauty salon and academy</t>
+          <t>Body Temple Gym 2</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6-A, Behind Maharwal Optical, Behind Vidhan Sabha Lal Kothi, Janpath Road, Friends Colony, Satya Vihar, Friends Colony, Krishna Nagar II, Lalkothi, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302015, India</t>
+          <t>Plot No.8, near prince hotel, Ambedkar Nagar, Tonk Phatak, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302015, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>098290 23927</t>
+          <t>096673 19072</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1242</v>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Social media only</t>
+        <v>632</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>No website</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Good social presence, missing a proper website</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/saundaryabeautysalon?igsh=dzJ4ZnZxd25zNjdt</t>
-        </is>
-      </c>
+          <t>Strong reviews, no way to showcase/book online</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
@@ -681,24 +677,24 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Sky Fitness - Best Gym in Mangyawas, Mansarovar, Jaipur</t>
+          <t>FitLife Gym Vaishali Nagar</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Maharani Garden Road, Mansarover, Rajat Path, Jaipur, Rajasthan 302020, India</t>
+          <t>4th Floor, Oppo- Khandelwal Dhabawalas, South, Gandhi Path Rd, Girnar Colony, Girnar Colony South, Chitrakoot, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302021, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>095880 37686</t>
+          <t>076888 91224</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>188</v>
+        <v>345</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
@@ -713,7 +709,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/skyfitnessjaipur</t>
+          <t>https://www.instagram.com/fitlifegym_vaishalinagar?utm_source=ig_web_button_share_sheet&amp;igsh=ZDNlZDc0MzIxNw==</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
@@ -723,29 +719,29 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>salons in Jaipur</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Sky Fitness - Best Gym In Ajmer Road, Jaipur</t>
+          <t>Beyond Brunette - A Luxury Salon</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1st Floor, ML Tower, Metro Piller No-01, Teja Circle, Gopalpura Bypass Rd, near Drom Marbel, Mohan Nagar, Mohru Nagar, Mansarovar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302020, India</t>
+          <t>Panchsheel Enclave, 79, Jawahar Lal Nehru Marg, behind Clarks Amer Hotel, Vishnu Enclave, Chandrakala Colony, Durgapura, Jaipur, Rajasthan 302018, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>075687 98310</t>
+          <t>077377 78513</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>118</v>
+        <v>321</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -760,7 +756,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/skyfitnessjaipur1</t>
+          <t>https://www.instagram.com/beyond_brunette?igsh=bGIyZ2xxamRpOW9q/</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -548,24 +548,24 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Handi restaurant jaipur</t>
+          <t>The Forresta Kitchen &amp; Bar</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Mirza Ismail Rd, opp. GPO, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>Devraj Niwas, Mirza Ismail Rd, near Shri Amarapur Setu, Barodia Scheme, Bani Park, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302006, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>098291 74873</t>
+          <t>090012 77999</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>13152</v>
+        <v>5068</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -586,29 +586,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>clinics in Jaipur</t>
+          <t>restaurants in Jaipur</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Divinity total skin care</t>
+          <t>Stardust Jaipur</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Kaveri Path, 21/280, Madhyam Marg, Mansarovar Sector 1, Mansarovar, Jaipur, Rajasthan 302020, India</t>
+          <t>Terrace floor, Signature Tower, Tonk Rd, Lalkothi, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302015, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>095711 33151</t>
+          <t>073575 48648</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1328</v>
+        <v>4817</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -629,29 +629,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>restaurants in Jaipur</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Body Temple Gym 2</t>
+          <t>The Magnolia</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Plot No.8, near prince hotel, Ambedkar Nagar, Tonk Phatak, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302015, India</t>
+          <t>Garden Theatre, Smriti Van, Jawahar Lal Nehru Marg, Jhalana Doongri, Jaipur, Rajasthan 302017, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>096673 19072</t>
+          <t>098284 75999</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>632</v>
+        <v>2696</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -677,41 +677,37 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>FitLife Gym Vaishali Nagar</t>
+          <t>FRIENDS GYM</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4th Floor, Oppo- Khandelwal Dhabawalas, South, Gandhi Path Rd, Girnar Colony, Girnar Colony South, Chitrakoot, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302021, India</t>
+          <t>Pno- 72, Sirsi marg, Engineer Colony, Bisnwala, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302034, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>076888 91224</t>
+          <t>099293 58094</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>345</v>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Social media only</t>
+        <v>853</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>No website</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Good social presence, missing a proper website</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/fitlifegym_vaishalinagar?utm_source=ig_web_button_share_sheet&amp;igsh=ZDNlZDc0MzIxNw==</t>
-        </is>
-      </c>
+          <t>Strong reviews, no way to showcase/book online</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
@@ -719,29 +715,29 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>salons in Jaipur</t>
+          <t>restaurants in Jaipur</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Beyond Brunette - A Luxury Salon</t>
+          <t>Blackout club in Jaipur</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Panchsheel Enclave, 79, Jawahar Lal Nehru Marg, behind Clarks Amer Hotel, Vishnu Enclave, Chandrakala Colony, Durgapura, Jaipur, Rajasthan 302018, India</t>
+          <t>8th &amp; 9th Floor,Landmark Building, Ashok Marg, Hotel Golden Oak, D38A, Ahinsa Cir, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>077377 78513</t>
+          <t>099281 16900</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>321</v>
+        <v>8226</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -756,7 +752,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beyond_brunette?igsh=bGIyZ2xxamRpOW9q/</t>
+          <t>https://www.facebook.com/blackoutjaipur/</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -548,24 +548,24 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>The Forresta Kitchen &amp; Bar</t>
+          <t>Brewlicious Rooftop Bar Restaurant in Jaipur</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Devraj Niwas, Mirza Ismail Rd, near Shri Amarapur Setu, Barodia Scheme, Bani Park, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302006, India</t>
+          <t>5, 10th floor, Gadi, Ajmer Rd, near kalyan jewellers, Hathroi, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>090012 77999</t>
+          <t>085048 00800</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5068</v>
+        <v>3436</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -591,24 +591,24 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Stardust Jaipur</t>
+          <t>Bootleggers Lounge &amp; Kitchen</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Terrace floor, Signature Tower, Tonk Rd, Lalkothi, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302015, India</t>
+          <t>B1/13, Gandhi Path W, Sector-1, Chitrakoot, Vaishali Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302021, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>073575 48648</t>
+          <t>083025 54055</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4817</v>
+        <v>2052</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -629,29 +629,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Jaipur</t>
+          <t>cafes in Jaipur</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>The Magnolia</t>
+          <t>Nibs Cafe &amp; Chocolataria</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Garden Theatre, Smriti Van, Jawahar Lal Nehru Marg, Jhalana Doongri, Jaipur, Rajasthan 302017, India</t>
+          <t>36, Sanjay Marg, Hathroi, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>098284 75999</t>
+          <t>0141 403 3858</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2696</v>
+        <v>1766</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -672,29 +672,29 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>restaurants in Jaipur</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>FRIENDS GYM</t>
+          <t>Hawk View Restaurant &amp; Bar</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Pno- 72, Sirsi marg, Engineer Colony, Bisnwala, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302034, India</t>
+          <t>76, Raja Mal Ka Talab, behind Kale Hanuman Ji Temple, Chandi Ki Taksal, J.D.A. Market, Brahampuri, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302002, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>099293 58094</t>
+          <t>094140 22447</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>853</v>
+        <v>1332</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -720,24 +720,24 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Blackout club in Jaipur</t>
+          <t>Khoje Restaurant</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8th &amp; 9th Floor,Landmark Building, Ashok Marg, Hotel Golden Oak, D38A, Ahinsa Cir, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>Durga marg, Patrakar Colony, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>099281 16900</t>
+          <t>086901 33358</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>8226</v>
+        <v>530</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/blackoutjaipur/</t>
+          <t>https://www.instagram.com/khoje.jaipur/?hl=en</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,12 +57,6 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -76,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -85,9 +79,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -543,29 +534,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Jaipur</t>
+          <t>gyms in Jaipur</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Brewlicious Rooftop Bar Restaurant in Jaipur</t>
+          <t>Ram's Fitness Club IMPACT</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>5, 10th floor, Gadi, Ajmer Rd, near kalyan jewellers, Hathroi, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>111/14, Mangalam, Sector 11 Rd, Kumbha Marg, Sanganer, Sector 11, Pratap Nagar, Jaipur, Rajasthan 302033, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>085048 00800</t>
+          <t>097722 78888</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3436</v>
+        <v>1284</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -586,29 +577,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Jaipur</t>
+          <t>salons in Jaipur</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Bootleggers Lounge &amp; Kitchen</t>
+          <t>Style &amp; Beauty World</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>B1/13, Gandhi Path W, Sector-1, Chitrakoot, Vaishali Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302021, India</t>
+          <t>station road, Flyover, near Jtm Mall, Income Tax Colony, Model Town, Jagatpura, Jaipur, Rajasthan 302017, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>083025 54055</t>
+          <t>088900 90042</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2052</v>
+        <v>303</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -629,29 +620,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>cafes in Jaipur</t>
+          <t>gyms in Jaipur</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Nibs Cafe &amp; Chocolataria</t>
+          <t>Let's Burn Gym</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>36, Sanjay Marg, Hathroi, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>B, arghan, first floor, TOWER-1, plot no R6, Sector 2, Sector-1, Vidyadhar Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302039, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0141 403 3858</t>
+          <t>099283 44474</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1766</v>
+        <v>243</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -672,29 +663,29 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Jaipur</t>
+          <t>cafes in Jaipur</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Hawk View Restaurant &amp; Bar</t>
+          <t>The house of coffee</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76, Raja Mal Ka Talab, behind Kale Hanuman Ji Temple, Chandi Ki Taksal, J.D.A. Market, Brahampuri, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302002, India</t>
+          <t>Ground Floor, F58, Sunder Marg, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>094140 22447</t>
+          <t>088241 41329</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1332</v>
+        <v>219</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -715,46 +706,42 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Jaipur</t>
+          <t>gyms in Jaipur</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Khoje Restaurant</t>
+          <t>WORKOUT ADDA ELITE THE LUXURY GYM</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Durga marg, Patrakar Colony, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>Pn 114 B, Krishna Nagar-B, Avadhpuri, Mahesh Nagar, Gopal Pura Mode, Jaipur, Rajasthan 302015, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>086901 33358</t>
+          <t>096800 38787</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>530</v>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Social media only</t>
+        <v>166</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>No website</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Good social presence, missing a proper website</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/khoje.jaipur/?hl=en</t>
-        </is>
-      </c>
+          <t>Strong reviews, no way to showcase/book online</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -534,29 +534,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>restaurants in Jaipur</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Ram's Fitness Club IMPACT</t>
+          <t>OTH Bistro &amp; Bakers Jaipur</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>111/14, Mangalam, Sector 11 Rd, Kumbha Marg, Sanganer, Sector 11, Pratap Nagar, Jaipur, Rajasthan 302033, India</t>
+          <t>E -145, Ramesh Marg, Durgadas Colony, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>097722 78888</t>
+          <t>0141 411 2232</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1284</v>
+        <v>5502</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -577,29 +577,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>salons in Jaipur</t>
+          <t>gyms in Jaipur</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Style &amp; Beauty World</t>
+          <t>The Fit Life Gym</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>station road, Flyover, near Jtm Mall, Income Tax Colony, Model Town, Jagatpura, Jaipur, Rajasthan 302017, India</t>
+          <t>B-493 JDA park, 80 Feet Rd, Krishna Nagar-B, Mahesh Nagar, Gopal Pura Mode, Jaipur, Rajasthan 302015, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>088900 90042</t>
+          <t>070147 55942</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>303</v>
+        <v>952</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -625,24 +625,24 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Let's Burn Gym</t>
+          <t>Infinity Club</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>B, arghan, first floor, TOWER-1, plot no R6, Sector 2, Sector-1, Vidyadhar Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302039, India</t>
+          <t>Infinity Club, Muhana Mandi Rd, near Kesar circle, behind Eden Garden, Mansarovar Extension, Hajiwala, Jaipur, Rajasthan 302020, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>099283 44474</t>
+          <t>089550 12924</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>243</v>
+        <v>840</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -663,29 +663,29 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>cafes in Jaipur</t>
+          <t>gyms in Jaipur</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>The house of coffee</t>
+          <t>CrossFit Gym</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Ground Floor, F58, Sunder Marg, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>A-9, Janta Store Cir, Bapu Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302015, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>088241 41329</t>
+          <t>079760 13905</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>219</v>
+        <v>330</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -706,29 +706,29 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>clinics in Jaipur</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>WORKOUT ADDA ELITE THE LUXURY GYM</t>
+          <t>Garg Poly Clinic</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Pn 114 B, Krishna Nagar-B, Avadhpuri, Mahesh Nagar, Gopal Pura Mode, Jaipur, Rajasthan 302015, India</t>
+          <t>D9, Meera Marg, Bani Park, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302016, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>096800 38787</t>
+          <t>0141 220 1422</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,12 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -70,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -79,6 +85,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -539,24 +548,24 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>OTH Bistro &amp; Bakers Jaipur</t>
+          <t>Sagar Ratna Restaurant</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>E -145, Ramesh Marg, Durgadas Colony, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>34, Subhash Marg, Panch Batti, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>0141 411 2232</t>
+          <t>0141 404 3536</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5502</v>
+        <v>2132</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -577,29 +586,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>salons in Jaipur</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>The Fit Life Gym</t>
+          <t>The beauty temple</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>B-493 JDA park, 80 Feet Rd, Krishna Nagar-B, Mahesh Nagar, Gopal Pura Mode, Jaipur, Rajasthan 302015, India</t>
+          <t>151, 151, Bhamasha Marg, Tirupati Balaji Nagar, Sector 8, Sector 6, Pratap Nagar, Jaipur, Rajasthan 302033, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>070147 55942</t>
+          <t>098757 58280</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>952</v>
+        <v>1362</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -620,29 +629,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>restaurants in Jaipur</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Infinity Club</t>
+          <t>Natraj Restaurant</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Infinity Club, Muhana Mandi Rd, near Kesar circle, behind Eden Garden, Mansarovar Extension, Hajiwala, Jaipur, Rajasthan 302020, India</t>
+          <t>Mirza Ismail Rd, Panch Batti, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>089550 12924</t>
+          <t>098290 64713</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>840</v>
+        <v>1179</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -663,29 +672,29 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>restaurants in Jaipur</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CrossFit Gym</t>
+          <t>14 Tables Restaurant</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>A-9, Janta Store Cir, Bapu Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302015, India</t>
+          <t>Lakshmi Complex, Mirza Ismail Rd, near G.P.O, Jayanti Market, New Colony, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>079760 13905</t>
+          <t>072300 42822</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>330</v>
+        <v>389</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -706,42 +715,46 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>clinics in Jaipur</t>
+          <t>restaurants in Jaipur</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Garg Poly Clinic</t>
+          <t>Monarch Restaurant</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>D9, Meera Marg, Bani Park, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302016, India</t>
+          <t>Holiday Inn, Sardar Patel Marg, Shivaji Nagar, Bais Godam, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0141 220 1422</t>
+          <t>0141 422 2444</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
         <v>4.5</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>597</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/monarch_holidayinnjaipur/</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,12 +57,6 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -76,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -85,9 +79,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -548,24 +539,24 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Sagar Ratna Restaurant</t>
+          <t>1135 AD</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>34, Subhash Marg, Panch Batti, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>1135 AD, Amber Palace, Jaleb Chowk, Devisinghpura, Amer, Jaipur, Jaipur Heritage (M Corp.) (Part), Rajasthan 302028, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>0141 404 3536</t>
+          <t>098290 37170</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2132</v>
+        <v>1887</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -586,29 +577,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>salons in Jaipur</t>
+          <t>cafes in Jaipur</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>The beauty temple</t>
+          <t>Cafesa - Pure Veg. Multi Cuisine Cafe and Restaurant</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>151, 151, Bhamasha Marg, Tirupati Balaji Nagar, Sector 8, Sector 6, Pratap Nagar, Jaipur, Rajasthan 302033, India</t>
+          <t>12, Shiv Marg, Kirti Nagar, Shyam Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302019, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>098757 58280</t>
+          <t>098290 17934</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1362</v>
+        <v>1463</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -629,29 +620,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Jaipur</t>
+          <t>cafes in Jaipur</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Natraj Restaurant</t>
+          <t>B&amp;B-Brew and Brunch</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Mirza Ismail Rd, Panch Batti, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>O-12, Ashok Marg, Patrakar Colony, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>098290 64713</t>
+          <t>073406 50765</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1179</v>
+        <v>1239</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -672,29 +663,29 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Jaipur</t>
+          <t>cafes in Jaipur</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>14 Tables Restaurant</t>
+          <t>Haveli Cafe - Jaipur Candle Light Dinner</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Lakshmi Complex, Mirza Ismail Rd, near G.P.O, Jayanti Market, New Colony, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>D, 219(B, Bhaskar Marg, Sindhi Colony, Bani Park, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302016, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>072300 42822</t>
+          <t>099836 30202</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>389</v>
+        <v>286</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -715,46 +706,42 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Jaipur</t>
+          <t>gyms in Jaipur</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Monarch Restaurant</t>
+          <t>The Workout Zone Gym and Fitness</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Holiday Inn, Sardar Patel Marg, Shivaji Nagar, Bais Godam, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>111/206 Vijay Path, Madhyam Marg, near VMart, Jhalana Chhod, Mansarovar, Jaipur, Rajasthan 302020, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0141 422 2444</t>
+          <t>079765 27674</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>597</v>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Social media only</t>
+        <v>205</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>No website</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Good social presence, missing a proper website</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/monarch_holidayinnjaipur/</t>
-        </is>
-      </c>
+          <t>Strong reviews, no way to showcase/book online</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,12 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -70,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -79,6 +85,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -534,29 +543,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Jaipur</t>
+          <t>cafes in Jaipur</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1135 AD</t>
+          <t>Cafe LazyMojo</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>1135 AD, Amber Palace, Jaleb Chowk, Devisinghpura, Amer, Jaipur, Jaipur Heritage (M Corp.) (Part), Rajasthan 302028, India</t>
+          <t>H1, H2, SL Marg, opp. Genpact Jaipur, Lal Bahadur Nagar, Malviya Nagar, Jaipur, Rajasthan 302018, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>098290 37170</t>
+          <t>098289 50999</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
         <v>4.3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1887</v>
+        <v>7054</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -582,24 +591,24 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Cafesa - Pure Veg. Multi Cuisine Cafe and Restaurant</t>
+          <t>The Tattoo Cafe &amp; Lounge</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>12, Shiv Marg, Kirti Nagar, Shyam Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302019, India</t>
+          <t>3rd floor, 30, Opposite Hawa Mahal, Hawa Mahal Rd, Badi Chaupar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302002, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>098290 17934</t>
+          <t>098280 65533</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1463</v>
+        <v>6536</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -625,24 +634,24 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>B&amp;B-Brew and Brunch</t>
+          <t>Café Bae</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>O-12, Ashok Marg, Patrakar Colony, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>A/1, 21, Sahkar Marg, Circle, near 22 Godown, C Scheme, Lalkothi, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>073406 50765</t>
+          <t>0141 274 4131</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1239</v>
+        <v>3748</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -668,24 +677,24 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Haveli Cafe - Jaipur Candle Light Dinner</t>
+          <t>Town Coffee 2.0</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>D, 219(B, Bhaskar Marg, Sindhi Colony, Bani Park, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302016, India</t>
+          <t>Plot no. 4, Durgadas Colony, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>099836 30202</t>
+          <t>077118 99994</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>286</v>
+        <v>2137</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -706,42 +715,46 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>cafes in Jaipur</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>The Workout Zone Gym and Fitness</t>
+          <t>Rangoon Coffee Brewery</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>111/206 Vijay Path, Madhyam Marg, near VMart, Jhalana Chhod, Mansarovar, Jaipur, Rajasthan 302020, India</t>
+          <t>Govt Hostel Chauraha, 5, Ajmer Rd, near Kalyan Jewellers, Gopalbari, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>079765 27674</t>
+          <t>095297 77778</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>574</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/rangoonjaipur?igshid=MWZjMTM2ODFkZg==</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -548,24 +548,24 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Cafe LazyMojo</t>
+          <t>Rustic by OTH</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>H1, H2, SL Marg, opp. Genpact Jaipur, Lal Bahadur Nagar, Malviya Nagar, Jaipur, Rajasthan 302018, India</t>
+          <t>H, 12, SL Marg, opposite जेनपैक्ट जयपुर, Lal Bahadur Nagar, Main, Malviya Nagar, Jaipur, Rajasthan 302018, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>098289 50999</t>
+          <t>0141 492 2208</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>7054</v>
+        <v>3830</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -586,29 +586,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cafes in Jaipur</t>
+          <t>clinics in Udaipur</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>The Tattoo Cafe &amp; Lounge</t>
+          <t>Redefine Aesthetics Clinic Udaipur</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>3rd floor, 30, Opposite Hawa Mahal, Hawa Mahal Rd, Badi Chaupar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302002, India</t>
+          <t>First Floor, Vinayak Complex-B, 19, Durga Nursery Rd, Shiv Park Colony, Compex, Shakti Nagar, Udaipur, Rajasthan 313002, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>098280 65533</t>
+          <t>078788 50277</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>6536</v>
+        <v>2739</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -634,24 +634,24 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Café Bae</t>
+          <t>Cafe Auberge</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>A/1, 21, Sahkar Marg, Circle, near 22 Godown, C Scheme, Lalkothi, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>House no 2, Jacob Rd, Mysore House/Achrol House Colony, Madrampur, Civil Lines, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302006, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0141 274 4131</t>
+          <t>096544 59062</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3748</v>
+        <v>434</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -677,24 +677,24 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Town Coffee 2.0</t>
+          <t>The Garden Cafe</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Plot no. 4, Durgadas Colony, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>VQPF+P6W, Swej Farm Rd, S.B. Vihar, Govindpuri, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302019, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>077118 99994</t>
+          <t>072218 11062</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2137</v>
+        <v>314</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -720,24 +720,24 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Rangoon Coffee Brewery</t>
+          <t>Cafe &amp; Cream</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Govt Hostel Chauraha, 5, Ajmer Rd, near Kalyan Jewellers, Gopalbari, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>heritage boutique hotel, Sugan Niwas Palace, Vijay path, behind Sindhi Camp Bus Stand, near laxmi palace, Kanti Nagar, Sindhi Camp, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302006, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>095297 77778</t>
+          <t>096027 80077</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>574</v>
+        <v>387</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/rangoonjaipur?igshid=MWZjMTM2ODFkZg==</t>
+          <t>https://instagram.com/cafeandcream_</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -543,29 +543,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>cafes in Jaipur</t>
+          <t>salons in Udaipur</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Rustic by OTH</t>
+          <t>Champion Hair Salon</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>H, 12, SL Marg, opposite जेनपैक्ट जयपुर, Lal Bahadur Nagar, Main, Malviya Nagar, Jaipur, Rajasthan 302018, India</t>
+          <t>shrinath colony, Under Hotel Riviera, near pulla pullia, New Flora Complex Colony, Pulla Bhuwana, road, Udaipur (M Corp.) (Part), Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>0141 492 2208</t>
+          <t>096490 88841</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
         <v>4.6</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3830</v>
+        <v>1071</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -586,29 +586,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>clinics in Udaipur</t>
+          <t>salons in Udaipur</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Redefine Aesthetics Clinic Udaipur</t>
+          <t>Vaidavya Hair Salon</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>First Floor, Vinayak Complex-B, 19, Durga Nursery Rd, Shiv Park Colony, Compex, Shakti Nagar, Udaipur, Rajasthan 313002, India</t>
+          <t>196, Garh Magri, Pulla Bhuwana, Shobhagpura, Sobhagpura, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>078788 50277</t>
+          <t>098879 96116</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2739</v>
+        <v>543</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -629,29 +629,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>cafes in Jaipur</t>
+          <t>clinics in Udaipur</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Cafe Auberge</t>
+          <t>Dr Nilesh Patira jain physician✅ BEST PHYSICIAN IN TOWN</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>House no 2, Jacob Rd, Mysore House/Achrol House Colony, Madrampur, Civil Lines, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302006, India</t>
+          <t>TRIVANTA hospital Near hotel Howard Johnson Meera nagar, C Block, Pahada, Bhuwana, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>096544 59062</t>
+          <t>088241 82649</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -672,42 +672,46 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>cafes in Jaipur</t>
+          <t>salons in Udaipur</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>The Garden Cafe</t>
+          <t>Monsoon Salon</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>VQPF+P6W, Swej Farm Rd, S.B. Vihar, Govindpuri, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302019, India</t>
+          <t>56, First Floor, Amrit Shree, Ashok Nagar Main Rd, Digamber Jain Mandir, Shakti Nagar, Udaipur, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>072218 11062</t>
+          <t>080060 60606</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>314</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>684</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/monsoonsalon.udaipur?igsh=aTVkZTZ6N3pkMnd3</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
@@ -715,29 +719,29 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>cafes in Jaipur</t>
+          <t>clinics in Udaipur</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Cafe &amp; Cream</t>
+          <t>Aura Skin and Hair Clinic</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>heritage boutique hotel, Sugan Niwas Palace, Vijay path, behind Sindhi Camp Bus Stand, near laxmi palace, Kanti Nagar, Sindhi Camp, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302006, India</t>
+          <t>221, Hanuman Mandir Vali Gali, Sardarpura, Udaipur, Rajasthan 313004, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>096027 80077</t>
+          <t>097855 00336</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>387</v>
+        <v>527</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -752,7 +756,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/cafeandcream_</t>
+          <t>http://www.facebook.com/auraskinandhairclinic/</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,12 +57,6 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -76,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -85,9 +79,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -543,29 +534,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>salons in Udaipur</t>
+          <t>gyms in Jaipur</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Champion Hair Salon</t>
+          <t>CrossFit Gym Jagatpura</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>shrinath colony, Under Hotel Riviera, near pulla pullia, New Flora Complex Colony, Pulla Bhuwana, road, Udaipur (M Corp.) (Part), Rajasthan 313001, India</t>
+          <t>B-6, Royal Mart, 1st 2nd 3rd Floor, B-6, NRI Colony Rd, Ramnagariya, Jaipur, Rajasthan 302017, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>096490 88841</t>
+          <t>095218 02771</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1071</v>
+        <v>1039</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -591,24 +582,24 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Vaidavya Hair Salon</t>
+          <t>Champion Gal's Spa &amp; Man's salon</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>196, Garh Magri, Pulla Bhuwana, Shobhagpura, Sobhagpura, Rajasthan 313001, India</t>
+          <t>M.G. Colllege Road, Near hanuman Temple, Sardarpura, Bhopalpura, Udaipur, Rajasthan 313004, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>098879 96116</t>
+          <t>097990 88841</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>543</v>
+        <v>930</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -634,24 +625,24 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Dr Nilesh Patira jain physician✅ BEST PHYSICIAN IN TOWN</t>
+          <t>Maharana Bhupal Govt Hospital</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>TRIVANTA hospital Near hotel Howard Johnson Meera nagar, C Block, Pahada, Bhuwana, Rajasthan 313001, India</t>
+          <t>Chohtta Chetak Rd, City's Prime Health Care Area, Udaipur, Rajasthan 313004, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>088241 82649</t>
+          <t>0294 252 8811</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>427</v>
+        <v>816</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -672,46 +663,42 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>salons in Udaipur</t>
+          <t>clinics in Udaipur</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Monsoon Salon</t>
+          <t>The skin &amp; Nature care clinic</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>56, First Floor, Amrit Shree, Ashok Nagar Main Rd, Digamber Jain Mandir, Shakti Nagar, Udaipur, Rajasthan 313001, India</t>
+          <t>Kesar Vihar, New, Ashok Nagar Main Rd, Kharakua, Udaipur, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>080060 60606</t>
+          <t>085049 25688</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>684</v>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Social media only</t>
+        <v>257</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>No website</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Good social presence, missing a proper website</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/monsoonsalon.udaipur?igsh=aTVkZTZ6N3pkMnd3</t>
-        </is>
-      </c>
+          <t>Strong reviews, no way to showcase/book online</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
@@ -724,41 +711,37 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Aura Skin and Hair Clinic</t>
+          <t>Victoria Hospital</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>221, Hanuman Mandir Vali Gali, Sardarpura, Udaipur, Rajasthan 313004, India</t>
+          <t>Hospital Tiraya, Manwakheda, Eklingpura, Udaipur, Rajasthan 313003, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>097855 00336</t>
+          <t>091661 70905</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>527</v>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Social media only</t>
+        <v>218</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>No website</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Good social presence, missing a proper website</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>http://www.facebook.com/auraskinandhairclinic/</t>
-        </is>
-      </c>
+          <t>Strong reviews, no way to showcase/book online</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -534,29 +534,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>salons in Udaipur</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CrossFit Gym Jagatpura</t>
+          <t>Mayur Salon Spa N Institute - Salon in Udaipur</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>B-6, Royal Mart, 1st 2nd 3rd Floor, B-6, NRI Colony Rd, Ramnagariya, Jaipur, Rajasthan 302017, India</t>
+          <t>Hathipole, opp. Hotel Sandal Inn, Chetak Circle, Chamanpura, Udaipur, Rajasthan 313004, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>095218 02771</t>
+          <t>092514 12285</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1039</v>
+        <v>417</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -582,24 +582,24 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Champion Gal's Spa &amp; Man's salon</t>
+          <t>Looks Salon - Urban Square Mall Udaipur</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>M.G. Colllege Road, Near hanuman Temple, Sardarpura, Bhopalpura, Udaipur, Rajasthan 313004, India</t>
+          <t>Mini Anchor-2, First Floor, Urban Square Mall, Udyog Vihar, Plot No. F - 210 to 223, Gaurav Path, RICO industrial area, Suker, Udaipur, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>097990 88841</t>
+          <t>096496 45133</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>930</v>
+        <v>323</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -620,29 +620,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>clinics in Udaipur</t>
+          <t>salons in Udaipur</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Maharana Bhupal Govt Hospital</t>
+          <t>Ftv London salon academy Udaipur</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Chohtta Chetak Rd, City's Prime Health Care Area, Udaipur, Rajasthan 313004, India</t>
+          <t>2nd floor, of Royal Enfield showroom, 100 Feet Rd, Pulla Bhuwana, Shobhagpura, Sobhagpura, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0294 252 8811</t>
+          <t>073000 02997</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>816</v>
+        <v>297</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -663,29 +663,29 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>clinics in Udaipur</t>
+          <t>salons in Udaipur</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>The skin &amp; Nature care clinic</t>
+          <t>Taj Hair Salon &amp; Spa</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Kesar Vihar, New, Ashok Nagar Main Rd, Kharakua, Udaipur, Rajasthan 313001, India</t>
+          <t>Taj hair salon &amp; spa, Plot No 3, 100 Feet Rd, near hotel maharaj, Shobhagpura, Sobhagpura, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>085049 25688</t>
+          <t>099821 66677</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -706,29 +706,29 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>clinics in Udaipur</t>
+          <t>salons in Udaipur</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Victoria Hospital</t>
+          <t>The Shyam Salon and Academy</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Hospital Tiraya, Manwakheda, Eklingpura, Udaipur, Rajasthan 313003, India</t>
+          <t>opposite coffee culture cafe, Ratneshwar Colony, Pulla Bhuwana, Shobhagpura, Sobhagpura, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>091661 70905</t>
+          <t>082090 76837</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>218</v>
+        <v>103</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,12 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -70,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -79,6 +85,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -534,29 +543,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>salons in Udaipur</t>
+          <t>restaurants in Jaipur</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Mayur Salon Spa N Institute - Salon in Udaipur</t>
+          <t>Sethia's Danapani</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Hathipole, opp. Hotel Sandal Inn, Chetak Circle, Chamanpura, Udaipur, Rajasthan 313004, India</t>
+          <t>40, Jan Path, Kishan Nagar, Shyam Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302019, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>092514 12285</t>
+          <t>099505 13333</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>417</v>
+        <v>4931</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -582,24 +591,24 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Looks Salon - Urban Square Mall Udaipur</t>
+          <t>Shree Natwar Hair &amp; skin care Family salon</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Mini Anchor-2, First Floor, Urban Square Mall, Udyog Vihar, Plot No. F - 210 to 223, Gaurav Path, RICO industrial area, Suker, Udaipur, Rajasthan 313001, India</t>
+          <t>Shop 4, 5, New Navratan Rd, near Eden Court, Bedla, Bhuwana, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>096496 45133</t>
+          <t>098280 82922</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>323</v>
+        <v>1239</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -620,29 +629,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>salons in Udaipur</t>
+          <t>gyms in Udaipur</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Ftv London salon academy Udaipur</t>
+          <t>Strength Nation Fitness Club Gym</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2nd floor, of Royal Enfield showroom, 100 Feet Rd, Pulla Bhuwana, Shobhagpura, Sobhagpura, Rajasthan 313001, India</t>
+          <t>297, Block-B, extension scheme, opposite to women Police Station, near Chitrakoot Nagar, Shyam Nagar, Bhuwana, Roopnagar, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>073000 02997</t>
+          <t>073401 81213</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>297</v>
+        <v>732</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -668,24 +677,24 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Taj Hair Salon &amp; Spa</t>
+          <t>Heera salon academy ( unisex )</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Taj hair salon &amp; spa, Plot No 3, 100 Feet Rd, near hotel maharaj, Shobhagpura, Sobhagpura, Rajasthan 313001, India</t>
+          <t>road, 120 Feet Rd, Sector 5, Shanti Nagar, Hiran Magri, Udaipur, Rajasthan 313002, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>099821 66677</t>
+          <t>096023 28206</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -706,42 +715,42 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>salons in Udaipur</t>
+          <t>gyms in Jaipur</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>The Shyam Salon and Academy</t>
+          <t>The Core Fitness Gym</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>opposite coffee culture cafe, Ratneshwar Colony, Pulla Bhuwana, Shobhagpura, Sobhagpura, Rajasthan 313001, India</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>082090 76837</t>
-        </is>
-      </c>
+          <t>4th Floor, KB Tower, near Parnami Mandir, Gurunanakpura, Raja Park, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302004, India</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>375</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the.corefitness/?hl=en</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,12 +57,6 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -76,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -85,9 +79,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -543,29 +534,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Jaipur</t>
+          <t>salons in Udaipur</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Sethia's Danapani</t>
+          <t>Darpan Beauty Parlour</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>40, Jan Path, Kishan Nagar, Shyam Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302019, India</t>
+          <t>Main road, opp. Guru Nanak Girl's College, behind Shiv Mandir, Nokha, Sector 4, Gayariawas, Hiran Magri, Udaipur, Rajasthan 313002, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>099505 13333</t>
+          <t>097847 45470</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4931</v>
+        <v>946</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -586,29 +577,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>salons in Udaipur</t>
+          <t>gyms in Udaipur</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Shree Natwar Hair &amp; skin care Family salon</t>
+          <t>Gymnation by Shashikant</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Shop 4, 5, New Navratan Rd, near Eden Court, Bedla, Bhuwana, Rajasthan 313001, India</t>
+          <t>2nd floor, University Rd, above neha nursing home, North Ayad, Ayad, Pahada, Udaipur, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>098280 82922</t>
+          <t>070236 62725</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1239</v>
+        <v>352</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -634,24 +625,24 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Strength Nation Fitness Club Gym</t>
+          <t>Delta Fitness</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>297, Block-B, extension scheme, opposite to women Police Station, near Chitrakoot Nagar, Shyam Nagar, Bhuwana, Roopnagar, Rajasthan 313001, India</t>
+          <t>30/31, Gokul Village Rd, Rk puram, Sector 9, Udaipur, Gordhan Vilas Rural, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>073401 81213</t>
+          <t>077428 09982</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>732</v>
+        <v>333</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -677,24 +668,24 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Heera salon academy ( unisex )</t>
+          <t>Looks Salon - Urban Square Mall Udaipur</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>road, 120 Feet Rd, Sector 5, Shanti Nagar, Hiran Magri, Udaipur, Rajasthan 313002, India</t>
+          <t>Mini Anchor-2, First Floor, Urban Square Mall, Udyog Vihar, Plot No. F - 210 to 223, Gaurav Path, RICO industrial area, Sukher, Udaipur, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>096023 28206</t>
+          <t>096496 45133</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -715,42 +706,42 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>gyms in Udaipur</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>The Core Fitness Gym</t>
+          <t>Gym World</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4th Floor, KB Tower, near Parnami Mandir, Gurunanakpura, Raja Park, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302004, India</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
+          <t>301, Creative Plaza, University Rd, North Ayad, Ayad, Pahada, Udaipur, Rajasthan 313001, India</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>098281 12123</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>375</v>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Social media only</t>
+        <v>198</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>No website</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Good social presence, missing a proper website</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/the.corefitness/?hl=en</t>
-        </is>
-      </c>
+          <t>Strong reviews, no way to showcase/book online</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,12 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -70,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -79,6 +85,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -534,29 +543,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>salons in Udaipur</t>
+          <t>restaurants in Udaipur</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Darpan Beauty Parlour</t>
+          <t>Verandah by the Lake</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Main road, opp. Guru Nanak Girl's College, behind Shiv Mandir, Nokha, Sector 4, Gayariawas, Hiran Magri, Udaipur, Rajasthan 313002, India</t>
+          <t>8, Jethiyon Ka Akhara, Near, Chandpole Bridge, Ambamata, Udaipur, Rajasthan 313004, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>097847 45470</t>
+          <t>089551 42160</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>946</v>
+        <v>2599</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -577,29 +586,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>gyms in Udaipur</t>
+          <t>restaurants in Udaipur</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Gymnation by Shashikant</t>
+          <t>South Grills Rooftop Restaurant</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2nd floor, University Rd, above neha nursing home, North Ayad, Ayad, Pahada, Udaipur, Rajasthan 313001, India</t>
+          <t>16, Bajarang Marg, Ghat Road, Outside Chandpole, Ambrai, Ambamata, Udaipur, Rajasthan 313004, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>070236 62725</t>
+          <t>086194 66385</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>352</v>
+        <v>514</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -625,24 +634,24 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Delta Fitness</t>
+          <t>The Workout Wala</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>30/31, Gokul Village Rd, Rk puram, Sector 9, Udaipur, Gordhan Vilas Rural, Rajasthan 313001, India</t>
+          <t>Woodland Square, Amal Ka Kanta Rd, near Police Thana, Kanji Ka Hata, Surajpole, Brahmpuri, Udaipur, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>077428 09982</t>
+          <t>099504 71921</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>333</v>
+        <v>413</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -663,42 +672,46 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>salons in Udaipur</t>
+          <t>gyms in Udaipur</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Looks Salon - Urban Square Mall Udaipur</t>
+          <t>JK THE MEDICAL GYM</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Mini Anchor-2, First Floor, Urban Square Mall, Udyog Vihar, Plot No. F - 210 to 223, Gaurav Path, RICO industrial area, Sukher, Udaipur, Rajasthan 313001, India</t>
+          <t>Krishna Vatika, Near, RK Circle, Pulan, Pulla Bhuwana, Rupsagar, Udaipur (M Corp.) (Part), Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>096496 45133</t>
+          <t>099289 81863</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
         <v>4.7</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>323</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>525</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jkmedicalgym?utm_source=ig_web_button_share_sheet&amp;igsh=ZDNlZDc0MzIxNw==</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
@@ -711,37 +724,41 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Gym World</t>
+          <t>Pro Fitness Studio</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>301, Creative Plaza, University Rd, North Ayad, Ayad, Pahada, Udaipur, Rajasthan 313001, India</t>
+          <t>338, Madri industry road, U.L.T.Colony, Udaipur, Rajasthan 313003, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>098281 12123</t>
+          <t>096022 33710</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>184</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pro_fitness_studio_1.0?igsh=eDAzY2YwemFlN3Jj</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -543,29 +543,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Udaipur</t>
+          <t>clinics in Udaipur</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Verandah by the Lake</t>
+          <t>Kalpana Nursing Home</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>8, Jethiyon Ka Akhara, Near, Chandpole Bridge, Ambamata, Udaipur, Rajasthan 313004, India</t>
+          <t>214-C, Sardarpura, Udaipur, Rajasthan 313004, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>089551 42160</t>
+          <t>093514 56733</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2599</v>
+        <v>2236</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -586,29 +586,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Udaipur</t>
+          <t>restaurants in Jaipur</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>South Grills Rooftop Restaurant</t>
+          <t>Rustic - Inspired Kitchen</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>16, Bajarang Marg, Ghat Road, Outside Chandpole, Ambrai, Ambamata, Udaipur, Rajasthan 313004, India</t>
+          <t>G-3, Ground Floor, UKMS, AURUM, Tilak Marg, near CBI office, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302005, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>086194 66385</t>
+          <t>099285 97479</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>514</v>
+        <v>1597</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -634,24 +634,24 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>The Workout Wala</t>
+          <t>Fit Liv Gym</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Woodland Square, Amal Ka Kanta Rd, near Police Thana, Kanji Ka Hata, Surajpole, Brahmpuri, Udaipur, Rajasthan 313001, India</t>
+          <t>Savita Nagar, near Parshuram Marg, Santosh Nagar, Gayariawas, Choraha, Udaipur, Rajasthan 313002, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>099504 71921</t>
+          <t>077372 79764</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>413</v>
+        <v>206</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -672,29 +672,25 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>gyms in Udaipur</t>
+          <t>restaurants in Jaipur</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>JK THE MEDICAL GYM</t>
+          <t>Jaipur Courtyard</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Krishna Vatika, Near, RK Circle, Pulan, Pulla Bhuwana, Rupsagar, Udaipur (M Corp.) (Part), Rajasthan 313001, India</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>099289 81863</t>
-        </is>
-      </c>
+          <t>Gupta Garden, Amer Rd, Govind Nagar West, Brahampuri, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302002, India</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>525</v>
+        <v>2184</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
@@ -709,7 +705,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jkmedicalgym?utm_source=ig_web_button_share_sheet&amp;igsh=ZDNlZDc0MzIxNw==</t>
+          <t>https://www.instagram.com/jaipur_courtyard/?hl=en</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
@@ -719,29 +715,29 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>gyms in Udaipur</t>
+          <t>cafes in Jaipur</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Pro Fitness Studio</t>
+          <t>Jaipur Vista Cafe</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>338, Madri industry road, U.L.T.Colony, Udaipur, Rajasthan 313003, India</t>
+          <t>2nd and 3rd Floor, 34, Temple Amrit Raghunath, Dhabai Ji Ka Rasta, opposite Hawa Mahal, Badi Chaupar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302002, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>096022 33710</t>
+          <t>099283 91150</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>184</v>
+        <v>287</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -756,7 +752,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pro_fitness_studio_1.0?igsh=eDAzY2YwemFlN3Jj</t>
+          <t>https://www.instagram.com/jaipur.vista111/</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>

--- a/client_data/client_1239/leads.xlsx
+++ b/client_data/client_1239/leads.xlsx
@@ -543,29 +543,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>clinics in Udaipur</t>
+          <t>restaurants in Udaipur</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Kalpana Nursing Home</t>
+          <t>TMV Rooftop Restaurant Pure Veg</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>214-C, Sardarpura, Udaipur, Rajasthan 313004, India</t>
+          <t>The Mangal View Residency, Sharma Colony, 12, Rajasthan Mahila Vidyalaya Rd, Old City, Brahmpuri, Udaipur, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>093514 56733</t>
+          <t>092516 67403</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2236</v>
+        <v>1441</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -586,29 +586,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Jaipur</t>
+          <t>restaurants in Udaipur</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Rustic - Inspired Kitchen</t>
+          <t>Terra Udaipur</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>G-3, Ground Floor, UKMS, AURUM, Tilak Marg, near CBI office, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302005, India</t>
+          <t>4th Floor, 25, Nav Ghat, Near, City Palace Rd, Old City, Silawatwari, Udaipur, Rajasthan 313004, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>099285 97479</t>
+          <t>079769 62722</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1597</v>
+        <v>429</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -634,24 +634,24 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Fit Liv Gym</t>
+          <t>PRIME ORA FITNESS GYM</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Savita Nagar, near Parshuram Marg, Santosh Nagar, Gayariawas, Choraha, Udaipur, Rajasthan 313002, India</t>
+          <t>13, Kheda Cir, Sector 14, Savina, Udaipur, Gordhan Vilas Rural, Rajasthan 313002, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>077372 79764</t>
+          <t>070730 67755</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -672,42 +672,42 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Jaipur</t>
+          <t>gyms in Udaipur</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Jaipur Courtyard</t>
+          <t>MEDILIFE FITNESS CLUB</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Gupta Garden, Amer Rd, Govind Nagar West, Brahampuri, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302002, India</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr"/>
+          <t>427, second floor, sec 6, Veena Nagar, Hiran Magri, Udaipur, Rajasthan 313002, India</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>078690 53353</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2184</v>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Social media only</t>
+        <v>41</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>No website</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Good social presence, missing a proper website</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/jaipur_courtyard/?hl=en</t>
-        </is>
-      </c>
+          <t>Strong reviews, no way to showcase/book online</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
@@ -715,29 +715,29 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>cafes in Jaipur</t>
+          <t>restaurants in Jaipur</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Jaipur Vista Cafe</t>
+          <t>Miroh Jaipur</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2nd and 3rd Floor, 34, Temple Amrit Raghunath, Dhabai Ji Ka Rasta, opposite Hawa Mahal, Badi Chaupar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302002, India</t>
+          <t>2nd Floor, Maya Mansion, Mirza Ismail Rd, opp. GPO, C Scheme, Ashok Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>099283 91150</t>
+          <t>096800 74873</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>287</v>
+        <v>550</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jaipur.vista111/</t>
+          <t>https://www.instagram.com/miroh.jaipur/</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
